--- a/data/out/variants/v5_no_fuel_and_cost/raw_v5_no_fuel_and_cost.xlsx
+++ b/data/out/variants/v5_no_fuel_and_cost/raw_v5_no_fuel_and_cost.xlsx
@@ -526,19 +526,19 @@
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>0.4247625960098906</v>
+        <v>0.4247625960098811</v>
       </c>
       <c r="G2" t="n">
-        <v>213.5415046339081</v>
+        <v>213.5415046339086</v>
       </c>
       <c r="H2" t="n">
-        <v>144552.4220120525</v>
+        <v>144552.4220120549</v>
       </c>
       <c r="I2" t="n">
-        <v>380.2005023826934</v>
+        <v>380.2005023826966</v>
       </c>
       <c r="J2" t="n">
-        <v>55.19221327997147</v>
+        <v>55.19221327996883</v>
       </c>
       <c r="K2" t="n">
         <v>48192</v>
@@ -550,7 +550,7 @@
         <v>9639</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05310773849487305</v>
+        <v>0.03830456733703613</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -580,19 +580,19 @@
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>0.4247527793683761</v>
+        <v>0.4247528229775477</v>
       </c>
       <c r="G3" t="n">
-        <v>213.5466172270425</v>
+        <v>213.5466411881268</v>
       </c>
       <c r="H3" t="n">
-        <v>144554.888853216</v>
+        <v>144554.8778945903</v>
       </c>
       <c r="I3" t="n">
-        <v>380.2037465007624</v>
+        <v>380.2037320892449</v>
       </c>
       <c r="J3" t="n">
-        <v>55.19545023827605</v>
+        <v>55.19552226894433</v>
       </c>
       <c r="K3" t="n">
         <v>48192</v>
@@ -604,7 +604,7 @@
         <v>9639</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04026556015014648</v>
+        <v>0.02799892425537109</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -634,19 +634,19 @@
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>0.4252912549576722</v>
+        <v>0.425197340808819</v>
       </c>
       <c r="G4" t="n">
-        <v>214.6565770774633</v>
+        <v>214.6664412554994</v>
       </c>
       <c r="H4" t="n">
-        <v>144419.5743724691</v>
+        <v>144443.1742246062</v>
       </c>
       <c r="I4" t="n">
-        <v>380.0257548804674</v>
+        <v>380.0568039446291</v>
       </c>
       <c r="J4" t="n">
-        <v>57.03089331184778</v>
+        <v>57.01970083088446</v>
       </c>
       <c r="K4" t="n">
         <v>48192</v>
@@ -658,7 +658,7 @@
         <v>9639</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2210564613342285</v>
+        <v>0.189138650894165</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -692,19 +692,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.4203748836498141</v>
+        <v>0.4203752893317301</v>
       </c>
       <c r="G5" t="n">
-        <v>215.7138938671095</v>
+        <v>215.7277944976046</v>
       </c>
       <c r="H5" t="n">
-        <v>145655.0179912809</v>
+        <v>145654.9160467566</v>
       </c>
       <c r="I5" t="n">
-        <v>381.6477669150979</v>
+        <v>381.6476333566823</v>
       </c>
       <c r="J5" t="n">
-        <v>56.52309939353503</v>
+        <v>56.54952024964874</v>
       </c>
       <c r="K5" t="n">
         <v>48192</v>
@@ -716,7 +716,7 @@
         <v>9639</v>
       </c>
       <c r="N5" t="n">
-        <v>18.62996649742126</v>
+        <v>14.7754385471344</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>-167.0475539056282</v>
+        <v>-167.0497828491669</v>
       </c>
     </row>
     <row r="6">
@@ -748,23 +748,23 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>{'max_depth': 10, 'min_samples_split': 10}</t>
+          <t>{'max_depth': 20, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>-0.1538584406666432</v>
+        <v>-0.1615439595730257</v>
       </c>
       <c r="G6" t="n">
-        <v>337.8932847133929</v>
+        <v>341.6999952280052</v>
       </c>
       <c r="H6" t="n">
-        <v>289955.1230508669</v>
+        <v>291886.430654703</v>
       </c>
       <c r="I6" t="n">
-        <v>538.4748119001175</v>
+        <v>540.2651484731391</v>
       </c>
       <c r="J6" t="n">
-        <v>66.46325380381965</v>
+        <v>70.24750631367714</v>
       </c>
       <c r="K6" t="n">
         <v>48192</v>
@@ -776,7 +776,7 @@
         <v>9639</v>
       </c>
       <c r="N6" t="n">
-        <v>3.757504940032959</v>
+        <v>3.082992315292358</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>-199.8385003062632</v>
+        <v>-199.35262367928</v>
       </c>
     </row>
     <row r="7">
@@ -808,23 +808,23 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 100}</t>
+          <t>{'max_depth': None, 'min_samples_split': 5, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>-0.1314784334879759</v>
+        <v>-0.1343318449434507</v>
       </c>
       <c r="G7" t="n">
-        <v>327.0966893246187</v>
+        <v>327.5050945054707</v>
       </c>
       <c r="H7" t="n">
-        <v>284331.2115668718</v>
+        <v>285048.2503651572</v>
       </c>
       <c r="I7" t="n">
-        <v>533.2271669437631</v>
+        <v>533.8991012964502</v>
       </c>
       <c r="J7" t="n">
-        <v>65.6325094677893</v>
+        <v>65.64255746663596</v>
       </c>
       <c r="K7" t="n">
         <v>48192</v>
@@ -836,7 +836,7 @@
         <v>9639</v>
       </c>
       <c r="N7" t="n">
-        <v>956.891676902771</v>
+        <v>851.4759161472321</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-196.976230667737</v>
+        <v>-197.0516076160525</v>
       </c>
     </row>
     <row r="8">
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.4877659709749874</v>
+        <v>0.488487863332579</v>
       </c>
       <c r="G8" t="n">
-        <v>182.7903466368367</v>
+        <v>182.5924499567828</v>
       </c>
       <c r="H8" t="n">
-        <v>128720.1927742353</v>
+        <v>128538.787170222</v>
       </c>
       <c r="I8" t="n">
-        <v>358.7759645994075</v>
+        <v>358.5230636517294</v>
       </c>
       <c r="J8" t="n">
-        <v>35.5887047508805</v>
+        <v>35.56024385335395</v>
       </c>
       <c r="K8" t="n">
         <v>48192</v>
@@ -896,7 +896,7 @@
         <v>9639</v>
       </c>
       <c r="N8" t="n">
-        <v>549.0222358703613</v>
+        <v>469.6038691997528</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>-164.2225411536513</v>
+        <v>-166.0139965476758</v>
       </c>
     </row>
     <row r="9">
@@ -932,19 +932,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.09012661978923597</v>
+        <v>0.07287718678228905</v>
       </c>
       <c r="G9" t="n">
-        <v>299.3490883949618</v>
+        <v>304.6447885810835</v>
       </c>
       <c r="H9" t="n">
-        <v>228643.6868003466</v>
+        <v>232978.3272499994</v>
       </c>
       <c r="I9" t="n">
-        <v>478.1670072269171</v>
+        <v>482.6782854552289</v>
       </c>
       <c r="J9" t="n">
-        <v>76.27385189975286</v>
+        <v>78.56851102729733</v>
       </c>
       <c r="K9" t="n">
         <v>48192</v>
@@ -956,7 +956,7 @@
         <v>9639</v>
       </c>
       <c r="N9" t="n">
-        <v>385.2582478523254</v>
+        <v>318.2035105228424</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>-248.8584453491461</v>
+        <v>-246.4958019542094</v>
       </c>
     </row>
     <row r="10">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.431845889366504</v>
+        <v>0.4291352811772713</v>
       </c>
       <c r="G10" t="n">
-        <v>243.2550881093178</v>
+        <v>244.4088620633439</v>
       </c>
       <c r="H10" t="n">
-        <v>142772.4487289905</v>
+        <v>143453.6022425857</v>
       </c>
       <c r="I10" t="n">
-        <v>377.8524165980555</v>
+        <v>378.7526927199142</v>
       </c>
       <c r="J10" t="n">
-        <v>70.08088213484299</v>
+        <v>70.94262736376659</v>
       </c>
       <c r="K10" t="n">
         <v>48192</v>
@@ -1016,7 +1016,7 @@
         <v>9639</v>
       </c>
       <c r="N10" t="n">
-        <v>2.599995136260986</v>
+        <v>3.473450422286987</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>-238.8483337187883</v>
+        <v>-238.3858717201695</v>
       </c>
     </row>
     <row r="11">
@@ -1048,23 +1048,23 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 612, 'learning_rate': 0.03517576744418695, 'max_depth': 3, 'subsample': 0.7306476438515299, 'colsample_bytree': 0.7371512737914546}</t>
+          <t>{'n_estimators': 456, 'learning_rate': 0.04125491713916763, 'max_depth': 3, 'subsample': 0.8289620075439558, 'colsample_bytree': 0.9947828702764736}</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.4280143014151055</v>
+        <v>0.4911082397358703</v>
       </c>
       <c r="G11" t="n">
-        <v>197.2433696441461</v>
+        <v>181.6917300206634</v>
       </c>
       <c r="H11" t="n">
-        <v>143735.2952245156</v>
+        <v>127880.3081612918</v>
       </c>
       <c r="I11" t="n">
-        <v>379.1243796229881</v>
+        <v>357.6035628475922</v>
       </c>
       <c r="J11" t="n">
-        <v>40.69100617518453</v>
+        <v>36.88774108103204</v>
       </c>
       <c r="K11" t="n">
         <v>48192</v>
@@ -1076,7 +1076,7 @@
         <v>9639</v>
       </c>
       <c r="N11" t="n">
-        <v>124.3753957748413</v>
+        <v>84.05866169929504</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1106,23 +1106,23 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 678, 'learning_rate': 0.015582758290717433, 'num_leaves': 31, 'min_child_samples': 47}</t>
+          <t>{'n_estimators': 466, 'learning_rate': 0.031166553078623278, 'num_leaves': 33, 'min_child_samples': 10}</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.3108680909624006</v>
+        <v>0.2992711122224376</v>
       </c>
       <c r="G12" t="n">
-        <v>230.1277583189434</v>
+        <v>232.764356929866</v>
       </c>
       <c r="H12" t="n">
-        <v>173173.1731041732</v>
+        <v>176087.3983497081</v>
       </c>
       <c r="I12" t="n">
-        <v>416.1408092270851</v>
+        <v>419.6276901608235</v>
       </c>
       <c r="J12" t="n">
-        <v>49.9357805376218</v>
+        <v>50.98307942049451</v>
       </c>
       <c r="K12" t="n">
         <v>48192</v>
@@ -1134,7 +1134,7 @@
         <v>9639</v>
       </c>
       <c r="N12" t="n">
-        <v>380.2190437316895</v>
+        <v>320.3220434188843</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1164,23 +1164,23 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>{'iterations': 715, 'learning_rate': 0.02556063598349147, 'depth': 4}</t>
+          <t>{'iterations': 701, 'learning_rate': 0.020608055474918455, 'depth': 4}</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.477286406474384</v>
+        <v>0.4871619884403537</v>
       </c>
       <c r="G13" t="n">
-        <v>187.4134331031415</v>
+        <v>185.4296670728882</v>
       </c>
       <c r="H13" t="n">
-        <v>131353.6210243562</v>
+        <v>128871.9686108354</v>
       </c>
       <c r="I13" t="n">
-        <v>362.4274010396512</v>
+        <v>358.9874212431898</v>
       </c>
       <c r="J13" t="n">
-        <v>39.70443174898138</v>
+        <v>39.86731926952277</v>
       </c>
       <c r="K13" t="n">
         <v>48192</v>
@@ -1192,7 +1192,7 @@
         <v>9639</v>
       </c>
       <c r="N13" t="n">
-        <v>368.499431848526</v>
+        <v>284.7246918678284</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1222,23 +1222,23 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 100}</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 500}</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.2658382676535073</v>
+        <v>0.2824949619159672</v>
       </c>
       <c r="G14" t="n">
-        <v>247.2376921568627</v>
+        <v>247.1293053179793</v>
       </c>
       <c r="H14" t="n">
-        <v>184488.7968395644</v>
+        <v>180303.1067546508</v>
       </c>
       <c r="I14" t="n">
-        <v>429.5215906558882</v>
+        <v>424.6211331936398</v>
       </c>
       <c r="J14" t="n">
-        <v>56.18176164280586</v>
+        <v>56.00085235948779</v>
       </c>
       <c r="K14" t="n">
         <v>48192</v>
@@ -1250,7 +1250,7 @@
         <v>9639</v>
       </c>
       <c r="N14" t="n">
-        <v>192.9909989833832</v>
+        <v>183.3088209629059</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>-171.8407867144726</v>
+        <v>-173.8553082502464</v>
       </c>
     </row>
     <row r="15">
@@ -1310,7 +1310,7 @@
         <v>9639</v>
       </c>
       <c r="N15" t="n">
-        <v>36.53486132621765</v>
+        <v>32.80784726142883</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>-175.9532236597531</v>
+        <v>-175.8782978278387</v>
       </c>
     </row>
     <row r="16">
@@ -1342,23 +1342,23 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>{'alpha': 0.01, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.001}</t>
+          <t>{'alpha': 0.001, 'hidden_layer_sizes': (128, 64), 'learning_rate_init': 0.001}</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.4613544990915923</v>
+        <v>0.3864899321097316</v>
       </c>
       <c r="G16" t="n">
-        <v>193.2264236801185</v>
+        <v>239.502633209781</v>
       </c>
       <c r="H16" t="n">
-        <v>135357.1781356977</v>
+        <v>154170.0272394698</v>
       </c>
       <c r="I16" t="n">
-        <v>367.9091982211069</v>
+        <v>392.64491240747</v>
       </c>
       <c r="J16" t="n">
-        <v>42.14951261780456</v>
+        <v>46.51223677716612</v>
       </c>
       <c r="K16" t="n">
         <v>48192</v>
@@ -1370,7 +1370,7 @@
         <v>9639</v>
       </c>
       <c r="N16" t="n">
-        <v>3225.524481296539</v>
+        <v>5505.951302528381</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>-168.168345664857</v>
+        <v>-170.992249675363</v>
       </c>
     </row>
   </sheetData>
